--- a/data/Resultados_finales_tesis/Mina_modelo_v4/Produccion_base/zona_norte/05C/P_red_gen_bat/elmo_data.xlsx
+++ b/data/Resultados_finales_tesis/Mina_modelo_v4/Produccion_base/zona_norte/05C/P_red_gen_bat/elmo_data.xlsx
@@ -3211,7 +3211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -3250,6 +3250,11 @@
           <t>g_max</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>vida_util</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -3287,6 +3292,11 @@
           <t>integer</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>años</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -3313,6 +3323,9 @@
       </c>
       <c r="G3" s="3" t="n">
         <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -3340,6 +3353,9 @@
       </c>
       <c r="G4" s="3" t="n">
         <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -3353,7 +3369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -3402,6 +3418,11 @@
           <t>h_max</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vida_util</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -3449,6 +3470,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>años</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -3479,6 +3505,9 @@
       </c>
       <c r="I3" s="34" t="n">
         <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
